--- a/public/downloads/banking/sources-and-uses-worksheet.xlsx
+++ b/public/downloads/banking/sources-and-uses-worksheet.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank worksheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Blank worksheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Example" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1460,7 +1460,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>About this example: a fictional dental practice buys and renovates its building using a structure like the SBA 504 program, which SBA describes as typically up to 50% from a senior lender, up to 40% from a CDC, and at least 10% from the borrower (sba.gov, as checked Sep 2026). Fees are left out for simplicity. Example data only.</t>
+          <t>About this example: a fictional dental practice buys and renovates its building using a structure like the SBA 504 program, which SBA describes as typically up to 50% from a senior lender, up to 40% from a CDC, and at least 10% from the borrower (sba.gov, as checked Oct 1, 2026). Fees are left out for simplicity. Example data only.</t>
         </is>
       </c>
     </row>
